--- a/stories/arbres/ATOM-REL.CON.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hervé joue dans le jardin avec maman. Eva a planté des graines. Un petit sillon est droit. Hervé passe trop près. Le sillon s'efface. Eva a les yeux mouillés. Elle est triste. Maman s'approche. Maman dit : tu peux dire pardon. Hervé dit : pardon, Eva. Maman dit : tu peux proposer un geste. Hervé prend la petite pelle. Il redessine le sillon. C'est un geste simple. Eva regarde. Elle reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.</t>
+          <t>Hervé joue dans le jardin avec maman. Eva a planté des graines. Un petit sillon est droit. Hervé passe trop près. Le sillon s'efface. Eva a les yeux mouillés. Elle est triste. Maman s'approche. Tu peux dire pardon. Pardon, Eva. Tu peux proposer un geste. Hervé prend la petite pelle. Il redessine le sillon. C'est un geste simple. Eva regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé joue dans le jardin avec maman. Eva a planté des graines. Un petit sillon est droit. Hervé passe trop près. Le sillon s'efface. Eva a les yeux mouillés. Elle est triste. Maman s'approche.
+maman|Tu peux dire pardon.
+enfant-m|Pardon, Eva.
+maman|Tu peux proposer un geste.
+narrateur|Hervé prend la petite pelle. Il redessine le sillon. C'est un geste simple. Eva regarde. Elle reste un peu triste.
+maman|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le sillon d'Eva s'est effacé. Que fait Hervé ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le sillon redevient droit. Maman reste assise près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le sillon d'Eva s'est effacé. Que fait Hervé ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Hervé a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Le sillon redevient droit. Maman reste assise près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hervé dit pardon et propose un geste</t>
+          <t>Le sillon après la pluie</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino efface le sillon de Nina. Il dit pardon et redessine le sillon. Ils plantent ensuite, tout doux. La peine de Nina reste un peu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hervé joue dans le jardin avec maman. Eva a planté des graines. Un petit sillon est droit. Hervé passe trop près. Le sillon s'efface. Eva a les yeux mouillés. Elle est triste. Maman s'approche. Tu peux dire pardon. Pardon, Eva. Tu peux proposer un geste. Hervé prend la petite pelle. Il redessine le sillon. C'est un geste simple. Eva regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.</t>
+          <t>La terre du jardin sent la pluie. Elle est froide et un peu grasse. Un sachet de graines fait un bruit de papier. Un vers rose se cache sous une motte. L'arrosoir goutte sur une feuille. La goutte est ronde, puis elle tombe. Un merle chante tout près, puis plus. Les genoux de Victorino sont un peu sales. Un caillou plat sert de porte-sachet. Il est gris, avec une ligne blanche. Le vent agite une feuille de salade. Tu as senti la terre, Victorino ? Oui, maman. Elle est froide. Je tiens le sachet. Les graines sont toutes petites. En ce moment, Nina a fait un sillon. Le sillon est droit, comme un trait. Victorino veut voir de près. Il passe trop près. Le sillon s'efface. La terre redevient un tas. Nina a les yeux mouillés. Elle est triste. Nina a de la peine, Victorino. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Victorino prend la petite pelle. La pelle est rouge, un peu humide. Il redessine le sillon. Je te le refais. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Victorino. Tu attends un peu ? Oui, papa. Le merle s'est tu. L'arrosoir goutte encore, loin. Nina pose sa main à plat sur la terre. Tu as le temps, Nina. Le sillon peut attendre une minute. Victorino pose la pelle à côté, tout doux. Plus tard, Nina pose une graine. La graine est beige, toute ronde. Victorino tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Victorino. C'est du bon travail. Nina a encore un peu de peine. C'est normal. Le sillon redevient droit. La terre brille un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hervé joue dans le jardin avec maman. Eva a planté des graines. Un petit sillon est droit. Hervé passe trop près. Le sillon s'efface. Eva a les yeux mouillés. Elle est triste. Maman s'approche.
+          <t>narrateur|La terre du jardin sent la pluie.
+narrateur|Elle est froide et un peu grasse.
+narrateur|Un sachet de graines fait un bruit de papier.
+narrateur|Un vers rose se cache sous une motte.
+narrateur|L'arrosoir goutte sur une feuille.
+narrateur|La goutte est ronde, puis elle tombe.
+narrateur|Un merle chante tout près, puis plus.
+narrateur|Les genoux de Victorino sont un peu sales.
+narrateur|Un caillou plat sert de porte-sachet.
+narrateur|Il est gris, avec une ligne blanche.
+narrateur|Le vent agite une feuille de salade.
+maman|Tu as senti la terre, Victorino ?
+enfant-m|Oui, maman.
+enfant-m|Elle est froide.
+papa|Je tiens le sachet.
+papa|Les graines sont toutes petites.
+narrateur|En ce moment, Nina a fait un sillon.
+narrateur|Le sillon est droit, comme un trait.
+narrateur|Victorino veut voir de près.
+narrateur|Il passe trop près.
+narrateur|Le sillon s'efface.
+narrateur|La terre redevient un tas.
+narrateur|Nina a les yeux mouillés.
+narrateur|Elle est triste.
+maman|Nina a de la peine, Victorino.
 maman|Tu peux dire pardon.
-enfant-m|Pardon, Eva.
+enfant-m|Pardon, Nina.
 maman|Tu peux proposer un geste.
-narrateur|Hervé prend la petite pelle. Il redessine le sillon. C'est un geste simple. Eva regarde. Elle reste un peu triste.
+narrateur|Victorino prend la petite pelle.
+narrateur|La pelle est rouge, un peu humide.
+narrateur|Il redessine le sillon.
+enfant-m|Je te le refais.
+narrateur|C'est un geste simple.
+narrateur|Nina regarde.
+narrateur|Elle reste un peu triste.
 maman|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Le pardon n'efface pas tout de suite.
+narrateur|Papa s'assoit près de Nina.
+papa|On laisse du temps, Victorino.
+papa|Tu attends un peu ?
+enfant-m|Oui, papa.
+narrateur|Le merle s'est tu.
+narrateur|L'arrosoir goutte encore, loin.
+narrateur|Nina pose sa main à plat sur la terre.
+papa|Tu as le temps, Nina.
+maman|Le sillon peut attendre une minute.
+narrateur|Victorino pose la pelle à côté, tout doux.
+narrateur|Plus tard, Nina pose une graine.
+narrateur|La graine est beige, toute ronde.
+narrateur|Victorino tend l'arrosoir.
+narrateur|Ils plantent doucement.
+narrateur|La peine reste un peu.
+maman|Tu as dit pardon.
+maman|Tu as proposé un geste.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+papa|Nina a encore un peu de peine.
+papa|C'est normal.
+narrateur|Le sillon redevient droit.
+narrateur|La terre brille un peu.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>merle,arrosoir</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le sillon d'Eva s'est effacé. Que fait Hervé ?</t>
+          <t>Le sillon de Nina s'est effacé. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le sillon d'Eva s'est effacé. Que fait Hervé ?</t>
+          <t>narrateur|Le sillon de Nina s'est effacé.
+narrateur|Que fait Victorino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hervé a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>Victorino a dit pardon. Il a proposé un geste. Il a redessiné le sillon. Bravo, Victorino. C'est du bon travail. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1744,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hervé a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>narrateur|Victorino a dit pardon.
+narrateur|Il a proposé un geste.
+narrateur|Il a redessiné le sillon.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+papa|La peine de Nina reste un peu.
+enfant-m|J'ai dit pardon.
+maman|Oui.
+maman|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le sillon redevient droit. Maman reste assise près d'eux.</t>
+          <t>Le sillon redevient droit. Nina pose encore une graine. On reste assis près de la terre ? Oui, maman. L'arrosoir est lourd, hein ? Un peu. La peine reste un peu. On laisse le temps. La terre sent toujours la pluie. Le vers rose ne se montre plus. Le caillou plat est encore chaud de main. On le laissera là. D'accord, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1920,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le sillon redevient droit. Maman reste assise près d'eux.</t>
+          <t>narrateur|Le sillon redevient droit.
+narrateur|Nina pose encore une graine.
+maman|On reste assis près de la terre ?
+enfant-m|Oui, maman.
+papa|L'arrosoir est lourd, hein ?
+enfant-m|Un peu.
+maman|La peine reste un peu.
+maman|On laisse le temps.
+papa|La terre sent toujours la pluie.
+narrateur|Le vers rose ne se montre plus.
+narrateur|Le caillou plat est encore chaud de main.
+papa|On le laissera là.
+enfant-m|D'accord, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai refait le sillon. Bravo. Tu as fait du bon travail. Une dernière goutte tombe de l'arrosoir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit pardon.
+enfant-m|J'ai refait le sillon.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Une dernière goutte tombe de l'arrosoir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La terre du jardin sent la pluie. Elle est froide et un peu grasse. Un sachet de graines fait un bruit de papier. Un vers rose se cache sous une motte. L'arrosoir goutte sur une feuille. La goutte est ronde, puis elle tombe. Un merle chante tout près, puis plus. Les genoux de Victorino sont un peu sales. Un caillou plat sert de porte-sachet. Il est gris, avec une ligne blanche. Le vent agite une feuille de salade. Tu as senti la terre, Victorino ? Oui, maman. Elle est froide. Je tiens le sachet. Les graines sont toutes petites. En ce moment, Nina a fait un sillon. Le sillon est droit, comme un trait. Victorino veut voir de près. Il passe trop près. Le sillon s'efface. La terre redevient un tas. Nina a les yeux mouillés. Elle est triste. Nina a de la peine, Victorino. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Victorino prend la petite pelle. La pelle est rouge, un peu humide. Il redessine le sillon. Je te le refais. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Victorino. Tu attends un peu ? Oui, papa. Le merle s'est tu. L'arrosoir goutte encore, loin. Nina pose sa main à plat sur la terre. Tu as le temps, Nina. Le sillon peut attendre une minute. Victorino pose la pelle à côté, tout doux. Plus tard, Nina pose une graine. La graine est beige, toute ronde. Victorino tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Victorino. C'est du bon travail. Nina a encore un peu de peine. C'est normal. Le sillon redevient droit. La terre brille un peu.</t>
+          <t>La terre du jardin sent la pluie. Elle est froide et un peu grasse. Un sachet de graines fait un bruit de papier. Un vers rose se cache sous une motte. L'arrosoir goutte sur une feuille. La goutte est ronde, puis elle tombe. Un merle chante tout près, puis plus. Les genoux de Victorino sont un peu sales. Un caillou plat sert de porte-sachet. Il est gris, avec une ligne blanche. Le vent agite une feuille de salade. Tu as senti la terre, Victorino ? Oui, maman. Elle est froide. Je tiens le sachet. Les graines sont toutes petites. En ce moment, Nina a fait un sillon. Le sillon est droit, comme un trait. Victorino veut voir de près. Il passe trop près. Le sillon s'efface. La terre redevient un tas. Nina a les yeux mouillés. Elle est triste. Nina a de la peine, Victorino. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Victorino prend la petite pelle. La pelle est rouge, un peu humide. Il redessine le sillon. Je te le refais. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Victorino. Tu attends un peu ? Oui, papa. Le merle s'est tu. L'arrosoir goutte encore, loin. Nina pose sa main à plat sur la terre. Tu as le temps, Nina. Le sillon peut attendre une minute. Victorino pose la pelle à côté, tout doux. Plus tard, Nina pose une graine. La graine est beige, toute ronde. Victorino tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Victorino. Nina a encore un peu de peine. C'est normal. Le sillon redevient droit. La terre brille un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hervé joue dans le jardin avec maman. Eva a planté des graines. Un petit sillon est droit. Hervé passe trop près. Le sillon s'efface. Eva a les yeux mouillés. Elle est triste. Maman s'approche. Maman dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Hervé dit : pardon, Eva. Maman dit : tu peux proposer un geste. Hervé prend la petite pelle. Il redessine le sillon. C'est un geste simple. Eva regarde. Elle reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Papa arrive. Il s'assoit près d'Eva. Hervé attend. Plus tard, Eva pose une graine. Hervé tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Maman laisse du temps à Eva.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La terre du jardin sent la pluie. Elle est froide et un peu grasse. Un sachet de graines fait un bruit de papier. Un vers rose se cache sous une motte. L'arrosoir goutte sur une feuille. La goutte est ronde, puis elle tombe. Un merle chante tout près, puis plus. Les genoux de Victorino sont un peu sales. Un caillou plat sert de porte-sachet. Il est gris, avec une ligne blanche. Le vent agite une feuille de salade. Tu as senti la terre, Victorino ? Oui, maman. Elle est froide. Je tiens le sachet. Les graines sont toutes petites. En ce moment, Nina a fait un sillon. Le sillon est droit, comme un trait. Victorino veut voir de près. Il passe trop près. Le sillon s'efface. La terre redevient un tas. Nina a les yeux mouillés. Elle est triste. Nina a de la peine, Victorino. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Victorino prend la petite pelle. La pelle est rouge, un peu humide. Il redessine le sillon. Je te le refais. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Victorino. Tu attends un peu ? Oui, papa. Le merle s'est tu. L'arrosoir goutte encore, loin. Nina pose sa main à plat sur la terre. Tu as le temps, Nina. Le sillon peut attendre une minute. Victorino pose la pelle à côté, tout doux. Plus tard, Nina pose une graine. La graine est beige, toute ronde. Victorino tend l'arrosoir. Ils plantent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Victorino. Nina a encore un peu de peine. C'est normal. Le sillon redevient droit. La terre brille un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 maman|Tu as dit pardon.
 maman|Tu as proposé un geste.
 maman|Bravo, Victorino.
-maman|C'est du bon travail.
 papa|Nina a encore un peu de peine.
 papa|C'est normal.
 narrateur|Le sillon redevient droit.
@@ -1420,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le sillon d'Eva s'est effacé. Que fait Hervé ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sillon de Nina s'est effacé. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1574,6 @@
 narrateur|Que fait Victorino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a dit pardon. Il a proposé un geste. Il a redessiné le sillon. Bravo, Victorino. C'est du bon travail. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Victorino a dit pardon. Il a proposé un geste. Il a redessiné le sillon. Bravo, Victorino. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hervé a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Il a proposé un geste. La peine reste un peu. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a dit pardon. Il a proposé un geste. Il a redessiné le sillon. Bravo, Victorino. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,14 +1746,12 @@
 narrateur|Il a proposé un geste.
 narrateur|Il a redessiné le sillon.
 maman|Bravo, Victorino.
-maman|C'est du bon travail.
 papa|La peine de Nina reste un peu.
 enfant-m|J'ai dit pardon.
 maman|Oui.
 maman|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le sillon redevient droit. Maman reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sillon redevient droit. Nina pose encore une graine. On reste assis près de la terre ? Oui, maman. L'arrosoir est lourd, hein ? Un peu. La peine reste un peu. On laisse le temps. La terre sent toujours la pluie. Le vers rose ne se montre plus. Le caillou plat est encore chaud de main. On le laissera là. D'accord, papa.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1931,6 @@
 enfant-m|D'accord, papa.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai refait le sillon. Bravo. Tu as fait du bon travail. Une dernière goutte tombe de l'arrosoir. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai refait le sillon. Bravo. Une dernière goutte tombe de l'arrosoir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai refait le sillon. Bravo. Une dernière goutte tombe de l'arrosoir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
           <t>enfant-m|J'ai dit pardon.
 enfant-m|J'ai refait le sillon.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Une dernière goutte tombe de l'arrosoir.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Une dernière goutte tombe de l'arrosoir.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hervé, Eva, maman, papa</t>
+          <t>Victorino, Nina, maman, papa</t>
         </is>
       </c>
     </row>
